--- a/artfynd/A 27506-2024 artfynd.xlsx
+++ b/artfynd/A 27506-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98542977</v>
+        <v>98542966</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R2" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -832,15 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98542965</v>
+        <v>98542970</v>
       </c>
       <c r="B3" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,26 +838,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>100051</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Sydfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus serotinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -889,10 +879,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R3" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -989,42 +979,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98542962</v>
+        <v>98542976</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>100087</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1042,14 +1027,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsnäs Ulvingebo, 65 m NNV, Ög</t>
+          <t>Sundsnäs Ulvingebo, 100 m NV, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531956.2176172147</v>
+        <v>531889</v>
       </c>
       <c r="R4" t="n">
-        <v>6427947.225955326</v>
+        <v>6427929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1105,7 +1090,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallbryn mot boningshus</t>
+          <t>Tallbryn mot ladugård</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1149,12 +1134,7 @@
         <v>98542959</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1203,10 +1183,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531956.2176172147</v>
+        <v>531956</v>
       </c>
       <c r="R5" t="n">
-        <v>6427947.225955326</v>
+        <v>6427947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1303,42 +1283,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98542972</v>
+        <v>98542969</v>
       </c>
       <c r="B6" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1360,10 +1335,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R6" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1460,15 +1435,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98542969</v>
+        <v>98542977</v>
       </c>
       <c r="B7" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,26 +1446,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1517,10 +1487,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R7" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1617,15 +1587,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98542973</v>
+        <v>98542962</v>
       </c>
       <c r="B8" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1652,7 +1617,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1670,14 +1635,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsnäs Ulvingebo, 100 m NV, Ög</t>
+          <t>Sundsnäs Ulvingebo, 65 m NNV, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531888.3728471316</v>
+        <v>531956</v>
       </c>
       <c r="R8" t="n">
-        <v>6427929.719741598</v>
+        <v>6427947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1733,7 +1698,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallbryn mot ladugård</t>
+          <t>Tallbryn mot boningshus</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1774,42 +1739,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98542961</v>
+        <v>98542973</v>
       </c>
       <c r="B9" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1827,14 +1787,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sundsnäs Ulvingebo, 65 m NNV, Ög</t>
+          <t>Sundsnäs Ulvingebo, 100 m NV, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531956.2176172147</v>
+        <v>531889</v>
       </c>
       <c r="R9" t="n">
-        <v>6427947.225955326</v>
+        <v>6427929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1890,7 +1850,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Tallbryn mot boningshus</t>
+          <t>Tallbryn mot ladugård</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1931,15 +1891,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98542957</v>
+        <v>98542961</v>
       </c>
       <c r="B10" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,26 +1902,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1988,10 +1943,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>531956.2176172147</v>
+        <v>531956</v>
       </c>
       <c r="R10" t="n">
-        <v>6427947.225955326</v>
+        <v>6427947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2088,15 +2043,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98542976</v>
+        <v>98542972</v>
       </c>
       <c r="B11" t="n">
-        <v>57495</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2104,26 +2054,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100087</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2145,10 +2095,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R11" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2245,15 +2195,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98542970</v>
+        <v>98542957</v>
       </c>
       <c r="B12" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på determinatörs verifiering</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2261,26 +2206,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100051</v>
+        <v>206002</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eptesicus serotinus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2298,14 +2243,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sundsnäs Ulvingebo, 100 m NV, Ög</t>
+          <t>Sundsnäs Ulvingebo, 65 m NNV, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>531888.3728471316</v>
+        <v>531956</v>
       </c>
       <c r="R12" t="n">
-        <v>6427929.719741598</v>
+        <v>6427947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2361,7 +2306,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallbryn mot ladugård</t>
+          <t>Tallbryn mot boningshus</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2402,15 +2347,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98542966</v>
+        <v>98542965</v>
       </c>
       <c r="B13" t="n">
-        <v>57482</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2418,26 +2358,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100015</v>
+        <v>206002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2459,10 +2399,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>531888.3728471316</v>
+        <v>531889</v>
       </c>
       <c r="R13" t="n">
-        <v>6427929.719741598</v>
+        <v>6427929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 27506-2024 artfynd.xlsx
+++ b/artfynd/A 27506-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -824,6 +829,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542966</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -976,6 +986,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1128,6 +1143,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542976</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1280,6 +1300,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542959</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1432,6 +1457,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542969</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1584,6 +1614,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542977</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1736,6 +1771,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542962</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1888,6 +1928,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542973</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2040,6 +2085,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542961</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2192,6 +2242,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542972</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2344,6 +2399,11 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542957</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2496,8 +2556,27 @@
           <t>Fladdermöss - gemensamt delprogram (regional miljöövervakning)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98542965</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>